--- a/prep_and_checklists/Peter and Sofia  /ORDER_GUIDE_Peter and Sofia  _Friday, March 20, 2026  _0.xlsx
+++ b/prep_and_checklists/Peter and Sofia  /ORDER_GUIDE_Peter and Sofia  _Friday, March 20, 2026  _0.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Peter and Sofia  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB8FFBC-4B2E-C24A-B5C2-7E556120F99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7275A06F-6DDA-D848-B254-49D4A4E5A8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1160" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="880" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="order_guide" sheetId="1" r:id="rId1"/>
     <sheet name="protein_order_guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="96">
   <si>
     <t xml:space="preserve">Event:Peter and Sofia   Date: Friday, March 20, 2026  </t>
   </si>
@@ -294,9 +307,6 @@
   </si>
   <si>
     <t>1 x 200g tin</t>
-  </si>
-  <si>
-    <t>2lbs</t>
   </si>
   <si>
     <t>1 side</t>
@@ -519,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -581,10 +591,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3651,7 +3657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.83203125" style="11" customWidth="1"/>
@@ -3726,11 +3732,15 @@
     </row>
     <row r="6" spans="1:11" ht="19" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
+      <c r="C6" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>92</v>
+      </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -3741,15 +3751,13 @@
     </row>
     <row r="7" spans="1:11" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="B7" s="23"/>
       <c r="C7" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>93</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D7" s="23"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
@@ -3760,13 +3768,15 @@
     </row>
     <row r="8" spans="1:11" ht="19" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="23"/>
+        <v>94</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>95</v>
+      </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
@@ -3776,16 +3786,6 @@
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:11" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>96</v>
-      </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -3795,12 +3795,6 @@
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:11" ht="19" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -3808,29 +3802,6 @@
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
-    </row>
-    <row r="11" spans="1:11" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
